--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.30014931410707</v>
+        <v>6.386274263542399</v>
       </c>
       <c r="D2" t="n">
-        <v>40.34428957278453</v>
+        <v>6.555947055577486</v>
       </c>
       <c r="E2" t="n">
-        <v>7.606808189212327</v>
+        <v>1.236106330747003</v>
       </c>
       <c r="F2" t="n">
-        <v>7.648248220149922</v>
+        <v>1.242840335774362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.56877189818658</v>
+        <v>8.37992543345532</v>
       </c>
       <c r="D3" t="n">
-        <v>51.71634174382516</v>
+        <v>8.403905533371589</v>
       </c>
       <c r="E3" t="n">
-        <v>7.606808189212327</v>
+        <v>1.236106330747003</v>
       </c>
       <c r="F3" t="n">
-        <v>7.648248220149922</v>
+        <v>1.242840335774362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.86527699591933</v>
+        <v>5.503107511836891</v>
       </c>
       <c r="D4" t="n">
-        <v>34.10519019589088</v>
+        <v>5.542093406832268</v>
       </c>
       <c r="E4" t="n">
-        <v>7.606808189212327</v>
+        <v>1.236106330747003</v>
       </c>
       <c r="F4" t="n">
-        <v>7.648248220149922</v>
+        <v>1.242840335774362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.23910939835931</v>
+        <v>5.888855277233389</v>
       </c>
       <c r="D5" t="n">
-        <v>36.37242604925041</v>
+        <v>5.910519233003193</v>
       </c>
       <c r="E5" t="n">
-        <v>7.606808189212327</v>
+        <v>1.236106330747003</v>
       </c>
       <c r="F5" t="n">
-        <v>7.648248220149922</v>
+        <v>1.242840335774362</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.2897656094754</v>
+        <v>7.847086911539752</v>
       </c>
       <c r="D6" t="n">
-        <v>48.84591683989631</v>
+        <v>7.937461486483151</v>
       </c>
       <c r="E6" t="n">
-        <v>7.606808189212327</v>
+        <v>1.236106330747003</v>
       </c>
       <c r="F6" t="n">
-        <v>7.648248220149922</v>
+        <v>1.242840335774362</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.31646098814011</v>
+        <v>8.663924910572769</v>
       </c>
       <c r="D7" t="n">
-        <v>53.93931249038176</v>
+        <v>8.765138279687037</v>
       </c>
       <c r="E7" t="n">
-        <v>7.606808189212327</v>
+        <v>1.236106330747003</v>
       </c>
       <c r="F7" t="n">
-        <v>7.648248220149922</v>
+        <v>1.242840335774362</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
